--- a/Result/profitability/6907.xlsx
+++ b/Result/profitability/6907.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM10"/>
+  <dimension ref="A1:AM11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1700,6 +1700,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>6907</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>963</v>
+      </c>
+      <c r="D11" t="n">
+        <v>578</v>
+      </c>
+      <c r="E11" t="n">
+        <v>385</v>
+      </c>
+      <c r="F11" t="n">
+        <v>39.97</v>
+      </c>
+      <c r="G11" t="n">
+        <v>186</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>19.28%</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>190</v>
+      </c>
+      <c r="K11" t="n">
+        <v>175</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="N11" t="n">
+        <v>34.29625</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.405172413793104</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>4.859999999999999</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.1384221019652521</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>4.936170212765957</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.1967065868263473</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK11" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
